--- a/data/trans_dic/P34A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P34A_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre</t>
+          <t>Población que no realiza actividad física en su tiempo libre (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,07; 41,18</t>
+          <t>29,93; 42,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,86; 29,81</t>
+          <t>19,36; 30,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,95; 38,1</t>
+          <t>26,79; 38,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36,17; 49,02</t>
+          <t>35,29; 48,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,38; 39,59</t>
+          <t>28,14; 39,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,38; 42,23</t>
+          <t>30,39; 42,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,54; 47,45</t>
+          <t>35,65; 47,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45,15; 55,27</t>
+          <t>45,31; 55,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,81; 39,34</t>
+          <t>30,61; 39,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,58; 34,35</t>
+          <t>26,35; 34,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,59; 40,78</t>
+          <t>32,54; 41,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,79; 50,51</t>
+          <t>41,95; 50,19</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,13; 37,14</t>
+          <t>28,03; 37,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 25,34</t>
+          <t>17,94; 25,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,75; 33,96</t>
+          <t>25,63; 33,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,78; 44,21</t>
+          <t>32,56; 43,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,29; 47,34</t>
+          <t>38,75; 47,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,81; 39,52</t>
+          <t>30,98; 39,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,72; 41,21</t>
+          <t>32,85; 41,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,28; 56,64</t>
+          <t>48,88; 56,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,97; 41,47</t>
+          <t>34,95; 40,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,63; 31,63</t>
+          <t>25,55; 31,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,19; 36,22</t>
+          <t>30,41; 36,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,93; 48,8</t>
+          <t>41,77; 48,97</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,61; 47,89</t>
+          <t>36,38; 47,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,59; 23,48</t>
+          <t>14,62; 23,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,2; 36,84</t>
+          <t>26,62; 37,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,66; 42,31</t>
+          <t>31,74; 42,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,41; 46,26</t>
+          <t>35,31; 46,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,51; 24,0</t>
+          <t>15,41; 23,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,67; 42,33</t>
+          <t>31,53; 42,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,41; 44,17</t>
+          <t>34,95; 43,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,25; 44,96</t>
+          <t>37,27; 44,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,07; 22,13</t>
+          <t>16,31; 22,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,92; 38,23</t>
+          <t>31,15; 38,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,81; 41,48</t>
+          <t>34,61; 41,39</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,77; 43,56</t>
+          <t>33,63; 44,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,71; 32,59</t>
+          <t>23,65; 32,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 26,54</t>
+          <t>17,5; 26,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,23; 41,95</t>
+          <t>28,09; 42,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,86; 46,51</t>
+          <t>37,05; 46,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,72; 38,29</t>
+          <t>28,89; 38,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,07; 40,16</t>
+          <t>30,33; 40,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 49,98</t>
+          <t>23,53; 49,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,94; 43,81</t>
+          <t>36,8; 43,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,18; 34,09</t>
+          <t>27,4; 34,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,94; 32,0</t>
+          <t>25,1; 32,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,41; 44,67</t>
+          <t>28,18; 44,34</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,13; 56,58</t>
+          <t>42,5; 56,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,11; 34,99</t>
+          <t>22,13; 34,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,74; 40,79</t>
+          <t>28,55; 41,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 13,95</t>
+          <t>6,8; 13,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>60,33; 74,15</t>
+          <t>60,72; 73,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,04; 44,88</t>
+          <t>31,6; 45,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,89; 54,42</t>
+          <t>41,52; 55,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,47; 17,25</t>
+          <t>10,96; 17,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,98; 64,42</t>
+          <t>53,97; 63,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,7; 37,88</t>
+          <t>28,65; 37,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,37; 46,25</t>
+          <t>37,09; 46,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 14,35</t>
+          <t>9,82; 14,45</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31,83; 43,72</t>
+          <t>32,4; 43,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,3; 18,66</t>
+          <t>10,37; 18,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,75; 40,83</t>
+          <t>28,58; 40,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,0; 45,86</t>
+          <t>35,43; 46,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,3; 50,96</t>
+          <t>39,12; 51,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,87; 24,38</t>
+          <t>15,05; 24,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,89; 47,74</t>
+          <t>35,45; 47,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,8; 47,07</t>
+          <t>37,66; 47,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,38; 45,88</t>
+          <t>37,28; 46,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 20,23</t>
+          <t>13,66; 20,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33,99; 42,67</t>
+          <t>33,84; 42,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38,01; 45,43</t>
+          <t>37,51; 45,27</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,48; 48,78</t>
+          <t>40,64; 48,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,62; 24,1</t>
+          <t>17,26; 24,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,67; 43,68</t>
+          <t>35,71; 43,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,21; 32,37</t>
+          <t>24,54; 32,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>42,56; 50,53</t>
+          <t>42,36; 49,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,48; 29,16</t>
+          <t>22,46; 29,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,77; 49,97</t>
+          <t>42,19; 49,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,02; 42,06</t>
+          <t>15,25; 42,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,7; 48,38</t>
+          <t>42,61; 48,26</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,76; 25,68</t>
+          <t>21,09; 25,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40,59; 46,08</t>
+          <t>40,44; 46,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,57; 35,52</t>
+          <t>17,99; 35,52</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,68; 48,75</t>
+          <t>41,42; 48,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,95; 27,76</t>
+          <t>21,2; 27,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34,92; 41,62</t>
+          <t>34,74; 42,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,47; 32,22</t>
+          <t>10,69; 32,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>47,88; 55,55</t>
+          <t>47,94; 55,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,13; 40,03</t>
+          <t>32,75; 39,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,23; 52,22</t>
+          <t>45,12; 52,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,72; 38,79</t>
+          <t>32,83; 38,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45,98; 51,22</t>
+          <t>45,8; 50,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,16; 33,01</t>
+          <t>28,25; 33,21</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41,29; 46,49</t>
+          <t>41,07; 46,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,84; 34,03</t>
+          <t>17,17; 34,19</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39,54; 42,93</t>
+          <t>39,27; 42,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,05; 24,1</t>
+          <t>21,01; 23,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,17; 35,48</t>
+          <t>32,23; 35,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23,33; 33,88</t>
+          <t>23,82; 34,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44,33; 47,97</t>
+          <t>44,47; 47,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,29; 32,53</t>
+          <t>29,39; 32,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,96; 44,33</t>
+          <t>41,07; 44,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30,91; 41,08</t>
+          <t>30,79; 41,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42,41; 44,94</t>
+          <t>42,38; 44,89</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25,73; 27,8</t>
+          <t>25,69; 27,86</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37,04; 39,43</t>
+          <t>37,17; 39,57</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,08; 37,09</t>
+          <t>30,06; 36,99</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza actividad física en su tiempo libre</t>
+          <t>Población que no realiza actividad física en su tiempo libre (tasa de respuesta: 99,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80858; 110729</t>
+          <t>80469; 113151</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58545; 87848</t>
+          <t>57069; 90274</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76225; 111928</t>
+          <t>78700; 112886</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112646; 152665</t>
+          <t>109919; 151776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71088; 102769</t>
+          <t>73045; 103734</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87273; 121306</t>
+          <t>87294; 122808</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>102618; 136989</t>
+          <t>102929; 135882</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>130768; 160096</t>
+          <t>131230; 160070</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>162846; 207892</t>
+          <t>161796; 206376</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>154706; 199927</t>
+          <t>153348; 198657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>189803; 237513</t>
+          <t>189554; 238872</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>251163; 303592</t>
+          <t>252159; 301701</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>138201; 182487</t>
+          <t>137704; 182123</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90246; 128116</t>
+          <t>90679; 129114</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>129394; 170678</t>
+          <t>128826; 168520</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>169433; 228525</t>
+          <t>168284; 223453</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>192163; 237617</t>
+          <t>194496; 237921</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>161368; 206989</t>
+          <t>162279; 208315</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>171166; 215553</t>
+          <t>171843; 216034</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>248328; 291338</t>
+          <t>251433; 290495</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>347374; 411898</t>
+          <t>347124; 406112</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>263854; 325599</t>
+          <t>263032; 322982</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>309654; 371474</t>
+          <t>311870; 372982</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>432425; 503308</t>
+          <t>430766; 504995</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>116342; 152197</t>
+          <t>115604; 150088</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47273; 76102</t>
+          <t>47364; 74684</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86664; 117348</t>
+          <t>84794; 118564</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100059; 133705</t>
+          <t>100318; 134563</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>118778; 155155</t>
+          <t>118449; 154532</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52902; 81857</t>
+          <t>52535; 81426</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>106494; 142348</t>
+          <t>106048; 142901</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>123633; 154224</t>
+          <t>122011; 152853</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>243320; 293710</t>
+          <t>243488; 293883</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106860; 147152</t>
+          <t>108439; 147844</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>202458; 250353</t>
+          <t>203977; 251481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>231570; 275947</t>
+          <t>230198; 275305</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>120614; 155590</t>
+          <t>120123; 157262</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84750; 121600</t>
+          <t>88255; 121674</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65935; 98205</t>
+          <t>64747; 97050</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88056; 130870</t>
+          <t>87624; 131895</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>135866; 171415</t>
+          <t>136573; 172487</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>111707; 148948</t>
+          <t>112361; 149905</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>116475; 155524</t>
+          <t>117447; 155588</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>112523; 237752</t>
+          <t>111954; 236215</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>268075; 317902</t>
+          <t>267063; 318862</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>207141; 259753</t>
+          <t>208837; 261307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>188871; 242299</t>
+          <t>190106; 242317</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>215919; 351842</t>
+          <t>221932; 349251</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>83626; 109710</t>
+          <t>82415; 109148</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47012; 74405</t>
+          <t>47060; 73305</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60701; 86157</t>
+          <t>60300; 87590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12407; 24936</t>
+          <t>12160; 24427</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>120510; 148119</t>
+          <t>121284; 147715</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68151; 98557</t>
+          <t>69395; 98944</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91563; 118959</t>
+          <t>90763; 120598</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21774; 35872</t>
+          <t>22790; 35392</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212498; 253594</t>
+          <t>212455; 250774</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>124048; 163724</t>
+          <t>123822; 163163</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>160635; 198800</t>
+          <t>159410; 198892</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37209; 55482</t>
+          <t>37955; 55860</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>84900; 116631</t>
+          <t>86440; 116808</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28210; 51127</t>
+          <t>28407; 52031</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75645; 107439</t>
+          <t>75209; 106383</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94377; 123657</t>
+          <t>95541; 124749</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>107758; 139732</t>
+          <t>107281; 140124</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41654; 68269</t>
+          <t>42158; 68910</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>98020; 130391</t>
+          <t>96818; 128977</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>97178; 120997</t>
+          <t>96804; 122101</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>202246; 248223</t>
+          <t>201702; 249920</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>75570; 112058</t>
+          <t>75701; 111324</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>182274; 228824</t>
+          <t>181453; 226698</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>200192; 239257</t>
+          <t>197574; 238412</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>246096; 296552</t>
+          <t>247033; 297179</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>116647; 159486</t>
+          <t>114273; 159114</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>234166; 286765</t>
+          <t>234477; 286599</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>149957; 200488</t>
+          <t>152010; 201159</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>266498; 316393</t>
+          <t>265236; 312946</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>155748; 202006</t>
+          <t>155590; 202553</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>295678; 345468</t>
+          <t>291628; 345005</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>126948; 355535</t>
+          <t>128951; 355083</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>526955; 597002</t>
+          <t>525840; 595551</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>281225; 347858</t>
+          <t>285646; 347453</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>547056; 621039</t>
+          <t>545028; 621408</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>271954; 520228</t>
+          <t>263510; 520330</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>303354; 354825</t>
+          <t>301489; 355778</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>163252; 216292</t>
+          <t>165207; 215282</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>271920; 324062</t>
+          <t>270456; 327109</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>96993; 298523</t>
+          <t>99055; 296534</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>360611; 418334</t>
+          <t>361013; 415097</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>272960; 329826</t>
+          <t>269851; 328125</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>373654; 431406</t>
+          <t>372789; 430031</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>233616; 277002</t>
+          <t>234417; 276976</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>680956; 758612</t>
+          <t>678280; 753809</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>451464; 529149</t>
+          <t>452844; 532288</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>662538; 746043</t>
+          <t>659079; 742800</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>276330; 558288</t>
+          <t>281609; 560945</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1277681; 1387470</t>
+          <t>1269057; 1384498</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>720971; 825293</t>
+          <t>719512; 820113</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1091965; 1204174</t>
+          <t>1093989; 1211924</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>804984; 1168999</t>
+          <t>822048; 1173211</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1471330; 1592159</t>
+          <t>1475908; 1591174</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1042002; 1157285</t>
+          <t>1045472; 1157918</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1451762; 1571420</t>
+          <t>1455725; 1574322</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1129133; 1500600</t>
+          <t>1124899; 1504516</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2777688; 2943935</t>
+          <t>2775725; 2940722</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1796791; 1940903</t>
+          <t>1793702; 1945254</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2570329; 2735966</t>
+          <t>2579108; 2745765</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2136716; 2634551</t>
+          <t>2135725; 2627855</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P34A_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,93; 42,08</t>
+          <t>30,2; 41,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,36; 30,63</t>
+          <t>20,16; 30,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,79; 38,43</t>
+          <t>26,42; 38,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,29; 48,73</t>
+          <t>39,44; 50,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,14; 39,96</t>
+          <t>27,61; 39,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,39; 42,75</t>
+          <t>30,76; 42,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,65; 47,07</t>
+          <t>35,12; 47,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45,31; 55,27</t>
+          <t>45,59; 55,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,61; 39,05</t>
+          <t>30,94; 39,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,35; 34,13</t>
+          <t>26,22; 34,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,54; 41,01</t>
+          <t>32,52; 40,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,95; 50,19</t>
+          <t>44,34; 51,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,03; 37,07</t>
+          <t>28,48; 37,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,94; 25,54</t>
+          <t>17,9; 25,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,63; 33,53</t>
+          <t>25,68; 34,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,56; 43,23</t>
+          <t>33,91; 44,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,75; 47,4</t>
+          <t>38,55; 47,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,98; 39,77</t>
+          <t>30,72; 39,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,85; 41,3</t>
+          <t>32,87; 41,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,88; 56,47</t>
+          <t>49,15; 56,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,95; 40,89</t>
+          <t>35,15; 41,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,55; 31,38</t>
+          <t>26,01; 31,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,41; 36,37</t>
+          <t>30,48; 36,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,77; 48,97</t>
+          <t>43,1; 49,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,38; 47,23</t>
+          <t>35,89; 47,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,62; 23,05</t>
+          <t>14,97; 23,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,62; 37,22</t>
+          <t>27,11; 37,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,74; 42,58</t>
+          <t>32,12; 42,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,31; 46,07</t>
+          <t>35,08; 45,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,41; 23,88</t>
+          <t>15,26; 23,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,53; 42,49</t>
+          <t>31,83; 42,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,95; 43,78</t>
+          <t>35,76; 44,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,27; 44,99</t>
+          <t>37,22; 44,88</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,31; 22,23</t>
+          <t>15,92; 22,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,15; 38,4</t>
+          <t>30,82; 38,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,61; 41,39</t>
+          <t>35,49; 42,02</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,63; 44,03</t>
+          <t>33,69; 43,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,65; 32,61</t>
+          <t>22,91; 32,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,5; 26,23</t>
+          <t>17,46; 26,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,09; 42,28</t>
+          <t>27,54; 40,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,05; 46,8</t>
+          <t>36,77; 46,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,89; 38,54</t>
+          <t>28,27; 38,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,33; 40,17</t>
+          <t>29,69; 39,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,53; 49,65</t>
+          <t>34,4; 43,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,8; 43,94</t>
+          <t>36,51; 43,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,4; 34,29</t>
+          <t>27,45; 34,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,1; 32,0</t>
+          <t>24,94; 31,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,18; 44,34</t>
+          <t>33,34; 41,13</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,5; 56,29</t>
+          <t>42,12; 56,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,13; 34,48</t>
+          <t>22,02; 35,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,55; 41,47</t>
+          <t>28,78; 41,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,67</t>
+          <t>6,42; 13,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>60,72; 73,95</t>
+          <t>60,89; 75,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,6; 45,06</t>
+          <t>31,62; 44,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,52; 55,17</t>
+          <t>41,36; 55,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,96; 17,02</t>
+          <t>10,65; 16,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,97; 63,7</t>
+          <t>53,78; 63,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,65; 37,75</t>
+          <t>28,67; 38,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,09; 46,27</t>
+          <t>37,34; 46,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,45</t>
+          <t>9,73; 14,25</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,4; 43,79</t>
+          <t>32,22; 44,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,37; 18,99</t>
+          <t>10,37; 19,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,58; 40,43</t>
+          <t>29,54; 40,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,43; 46,27</t>
+          <t>37,23; 47,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,12; 51,1</t>
+          <t>38,69; 50,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,05; 24,61</t>
+          <t>14,9; 24,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,45; 47,22</t>
+          <t>36,05; 47,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37,66; 47,5</t>
+          <t>37,37; 47,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,28; 46,2</t>
+          <t>37,04; 45,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 20,09</t>
+          <t>13,7; 19,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33,84; 42,28</t>
+          <t>33,94; 42,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,51; 45,27</t>
+          <t>38,89; 46,29</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,64; 48,89</t>
+          <t>40,84; 49,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,26; 24,04</t>
+          <t>17,73; 24,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,71; 43,65</t>
+          <t>35,86; 43,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24,54; 32,48</t>
+          <t>24,89; 32,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>42,36; 49,98</t>
+          <t>42,08; 49,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,46; 29,24</t>
+          <t>22,53; 29,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,19; 49,91</t>
+          <t>42,48; 50,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,25; 42,0</t>
+          <t>37,51; 44,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,61; 48,26</t>
+          <t>42,85; 48,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,09; 25,65</t>
+          <t>20,64; 25,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40,44; 46,1</t>
+          <t>40,73; 46,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,99; 35,52</t>
+          <t>32,68; 37,89</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>41,42; 48,88</t>
+          <t>41,56; 49,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,2; 27,63</t>
+          <t>21,12; 27,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34,74; 42,01</t>
+          <t>34,97; 41,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,69; 32,01</t>
+          <t>26,92; 33,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>47,94; 55,12</t>
+          <t>47,7; 55,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,75; 39,83</t>
+          <t>33,19; 40,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,12; 52,05</t>
+          <t>44,91; 52,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,83; 38,79</t>
+          <t>32,41; 38,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45,8; 50,9</t>
+          <t>45,91; 51,05</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,25; 33,21</t>
+          <t>28,17; 33,14</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41,07; 46,29</t>
+          <t>41,04; 46,23</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,17; 34,19</t>
+          <t>30,48; 34,93</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39,27; 42,84</t>
+          <t>39,18; 42,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21,01; 23,94</t>
+          <t>21,01; 23,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32,23; 35,7</t>
+          <t>32,19; 35,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23,82; 34,0</t>
+          <t>31,71; 35,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44,47; 47,94</t>
+          <t>44,36; 47,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,39; 32,55</t>
+          <t>29,27; 32,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,07; 44,42</t>
+          <t>41,15; 44,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30,79; 41,18</t>
+          <t>39,14; 41,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42,38; 44,89</t>
+          <t>42,42; 44,95</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25,69; 27,86</t>
+          <t>25,74; 27,83</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37,17; 39,57</t>
+          <t>37,31; 39,61</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,06; 36,99</t>
+          <t>36,01; 38,11</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131640</t>
+          <t>143732</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>145597</t>
+          <t>160526</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>277237</t>
+          <t>304257</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80469; 113151</t>
+          <t>81202; 112339</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57069; 90274</t>
+          <t>59423; 88789</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78700; 112886</t>
+          <t>77613; 112658</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109919; 151776</t>
+          <t>125766; 159708</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>73045; 103734</t>
+          <t>71687; 103757</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87294; 122808</t>
+          <t>88352; 122558</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>102929; 135882</t>
+          <t>101389; 136180</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>131230; 160070</t>
+          <t>144103; 174222</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>161796; 206376</t>
+          <t>163531; 207085</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153348; 198657</t>
+          <t>152586; 199268</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>189554; 238872</t>
+          <t>189417; 236573</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>252159; 301701</t>
+          <t>281546; 327313</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196051</t>
+          <t>206915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>271267</t>
+          <t>290093</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>467318</t>
+          <t>497008</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>137704; 182123</t>
+          <t>139927; 182159</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90679; 129114</t>
+          <t>90496; 127764</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128826; 168520</t>
+          <t>129047; 170955</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>168284; 223453</t>
+          <t>179472; 233545</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>194496; 237921</t>
+          <t>193500; 239300</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>162279; 208315</t>
+          <t>160890; 206480</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>171843; 216034</t>
+          <t>171952; 217885</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>251433; 290495</t>
+          <t>268286; 310614</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>347124; 406112</t>
+          <t>349079; 408339</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>263032; 322982</t>
+          <t>267687; 324616</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>311870; 372982</t>
+          <t>312650; 374122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>430766; 504995</t>
+          <t>463395; 534451</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116156</t>
+          <t>117313</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>137850</t>
+          <t>142623</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>254006</t>
+          <t>259937</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>115604; 150088</t>
+          <t>114071; 150216</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>47364; 74684</t>
+          <t>48514; 74816</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84794; 118564</t>
+          <t>86353; 118428</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100318; 134563</t>
+          <t>101490; 135227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>118449; 154532</t>
+          <t>117670; 151769</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52535; 81426</t>
+          <t>52041; 81404</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>106048; 142901</t>
+          <t>107056; 141682</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>122011; 152853</t>
+          <t>127439; 158654</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>243488; 293883</t>
+          <t>243113; 293135</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108439; 147844</t>
+          <t>105871; 148423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>203977; 251481</t>
+          <t>201839; 250703</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>230198; 275305</t>
+          <t>238609; 282502</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108087</t>
+          <t>128279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>178372</t>
+          <t>164064</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>286458</t>
+          <t>292343</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>120123; 157262</t>
+          <t>120321; 156361</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88255; 121674</t>
+          <t>85491; 122509</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64747; 97050</t>
+          <t>64597; 96636</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87624; 131895</t>
+          <t>102594; 151281</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>136573; 172487</t>
+          <t>135528; 172950</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>112361; 149905</t>
+          <t>109938; 148570</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>117447; 155588</t>
+          <t>114965; 154139</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>111954; 236215</t>
+          <t>145168; 184539</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>267063; 318862</t>
+          <t>264923; 318380</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>208837; 261307</t>
+          <t>209204; 261802</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>190106; 242317</t>
+          <t>188849; 241684</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>221932; 349251</t>
+          <t>264857; 326774</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17608</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>46084</t>
+          <t>49767</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82415; 109148</t>
+          <t>81671; 110412</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47060; 73305</t>
+          <t>46826; 74578</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60300; 87590</t>
+          <t>60782; 88040</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12160; 24427</t>
+          <t>13213; 27015</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>121284; 147715</t>
+          <t>121638; 150230</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69395; 98944</t>
+          <t>69436; 97707</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90763; 120598</t>
+          <t>90413; 120217</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22790; 35392</t>
+          <t>24105; 38470</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212455; 250774</t>
+          <t>211713; 251267</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>123822; 163163</t>
+          <t>123909; 164888</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159410; 198892</t>
+          <t>160486; 200392</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37955; 55860</t>
+          <t>42045; 61575</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108991</t>
+          <t>114766</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>108977</t>
+          <t>113029</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>217968</t>
+          <t>227795</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86440; 116808</t>
+          <t>85961; 117510</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28407; 52031</t>
+          <t>28406; 52504</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75209; 106383</t>
+          <t>77732; 106755</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95541; 124749</t>
+          <t>100797; 129815</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>107281; 140124</t>
+          <t>106092; 138996</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42158; 68910</t>
+          <t>41718; 68235</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>96818; 128977</t>
+          <t>98459; 129823</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>96804; 122101</t>
+          <t>98554; 125331</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>201702; 249920</t>
+          <t>200398; 246086</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>75701; 111324</t>
+          <t>75925; 110692</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181453; 226698</t>
+          <t>182006; 227413</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>197574; 238412</t>
+          <t>207825; 247378</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174486</t>
+          <t>207487</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>261424</t>
+          <t>314867</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>435910</t>
+          <t>522354</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>247033; 297179</t>
+          <t>248257; 298360</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>114273; 159114</t>
+          <t>117386; 160621</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>234477; 286599</t>
+          <t>235452; 287437</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>152010; 201159</t>
+          <t>177807; 233181</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>265236; 312946</t>
+          <t>263486; 312777</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>155590; 202553</t>
+          <t>156092; 204473</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>291628; 345005</t>
+          <t>293633; 345863</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>128951; 355083</t>
+          <t>287534; 340116</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>525840; 595551</t>
+          <t>528802; 596617</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>285646; 347453</t>
+          <t>279663; 346016</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>545028; 621408</t>
+          <t>548989; 626060</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>263510; 520330</t>
+          <t>483838; 561057</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>213083</t>
+          <t>240946</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>255049</t>
+          <t>292727</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>468132</t>
+          <t>533674</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>301489; 355778</t>
+          <t>302495; 356858</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>165207; 215282</t>
+          <t>164509; 214983</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>270456; 327109</t>
+          <t>272293; 323189</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>99055; 296534</t>
+          <t>214170; 268830</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>361013; 415097</t>
+          <t>359253; 417985</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>269851; 328125</t>
+          <t>273455; 330551</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>372789; 430031</t>
+          <t>371064; 431806</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>234417; 276976</t>
+          <t>268742; 316595</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>678280; 753809</t>
+          <t>679848; 756046</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>452844; 532288</t>
+          <t>451562; 531225</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>659079; 742800</t>
+          <t>658600; 741822</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>281609; 560945</t>
+          <t>495296; 567450</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1066102</t>
+          <t>1178305</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1387012</t>
+          <t>1508830</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2453114</t>
+          <t>2687135</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1269057; 1384498</t>
+          <t>1266243; 1378935</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>719512; 820113</t>
+          <t>719529; 818528</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1093989; 1211924</t>
+          <t>1092772; 1209112</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>822048; 1173211</t>
+          <t>1117217; 1240274</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1475908; 1591174</t>
+          <t>1472231; 1591192</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1045472; 1157918</t>
+          <t>1041111; 1153592</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1455725; 1574322</t>
+          <t>1458520; 1578005</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1124899; 1504516</t>
+          <t>1458472; 1558289</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2775725; 2940722</t>
+          <t>2778487; 2944256</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1793702; 1945254</t>
+          <t>1797037; 1943348</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2579108; 2745765</t>
+          <t>2589110; 2748514</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2135725; 2627855</t>
+          <t>2610556; 2762835</t>
         </is>
       </c>
     </row>
